--- a/public/samples/debit-notes-without-item-sample-file.xlsx
+++ b/public/samples/debit-notes-without-item-sample-file.xlsx
@@ -2,19 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$1:$T$53</definedName>
+  </definedNames>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,82 +22,61 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>Sales GST 18</t>
+  </si>
+  <si>
+    <t>CGST</t>
+  </si>
+  <si>
+    <t>SGST</t>
+  </si>
+  <si>
+    <t>GST NO</t>
+  </si>
+  <si>
+    <t>PARTY A/C NAME</t>
+  </si>
+  <si>
+    <t>PLACE OF SUPPLY</t>
+  </si>
+  <si>
+    <t>GUJARAT</t>
+  </si>
+  <si>
+    <t>IGST</t>
+  </si>
+  <si>
+    <t>24ABCDE1234G1ZP</t>
+  </si>
+  <si>
+    <t>XYZ</t>
+  </si>
+  <si>
+    <t>SUPPLIER INV NO</t>
+  </si>
   <si>
     <t>INVOICE DATE</t>
   </si>
   <si>
-    <t>GST NO</t>
-  </si>
-  <si>
-    <t>PARTY A/C NAME</t>
-  </si>
-  <si>
-    <t>PLACE OF SUPPLY</t>
-  </si>
-  <si>
-    <t>NAME OF ITEM</t>
-  </si>
-  <si>
-    <t>QUANTITY</t>
-  </si>
-  <si>
-    <t>RATE</t>
-  </si>
-  <si>
     <t>AMOUNT</t>
   </si>
   <si>
-    <t>SGST</t>
-  </si>
-  <si>
-    <t>CGST</t>
-  </si>
-  <si>
-    <t>IGST</t>
-  </si>
-  <si>
     <t>TOTAL AMOUNT</t>
   </si>
   <si>
-    <t>1000LPH Online Rotameter</t>
-  </si>
-  <si>
-    <t>1000 Ltr Ss Storage Tank</t>
-  </si>
-  <si>
-    <t>1 1/2" x 1" Reduser</t>
-  </si>
-  <si>
-    <t>GUJARAT</t>
-  </si>
-  <si>
-    <t>SUPPLIER INV NO</t>
-  </si>
-  <si>
-    <t>PURCHASE LEDGER</t>
-  </si>
-  <si>
-    <t>24ABCDE1234G1ZP</t>
-  </si>
-  <si>
-    <t>A J PUMP &amp; TUBEWELL</t>
-  </si>
-  <si>
-    <t>PURCHASE  (LOCAL)</t>
-  </si>
-  <si>
-    <t>SHIVAM ENGINEERING</t>
+    <t>PARTICULARS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,8 +92,16 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF222222"/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -130,38 +115,23 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF002060"/>
         <bgColor indexed="34"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF002060"/>
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="34"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -184,35 +154,36 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -276,9 +247,9 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -311,9 +282,9 @@
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -493,210 +464,315 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:T51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" customWidth="1"/>
+    <col min="8" max="9" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.42578125" customWidth="1"/>
+    <col min="13" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="6" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="4">
         <v>44440</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1000</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <f>SUM(G2*9%)</f>
+        <v>90</v>
       </c>
       <c r="I2">
-        <v>1000</v>
+        <f>SUM(G2*9%)</f>
+        <v>90</v>
       </c>
       <c r="J2">
-        <f>I2*H2</f>
-        <v>1000</v>
-      </c>
-      <c r="K2">
-        <f>SUM(J2*9%)</f>
-        <v>90</v>
-      </c>
-      <c r="L2">
-        <f>SUM(J2*9%)</f>
-        <v>90</v>
-      </c>
-      <c r="M2">
         <v>0</v>
       </c>
-      <c r="N2" s="4">
-        <f>SUM(J2+K2+L2+M2)</f>
+      <c r="K2" s="3">
+        <f>SUM(G2+H2+I2+J2)</f>
         <v>1180</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="9">
-        <v>44440</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>2000</v>
-      </c>
-      <c r="J3">
-        <v>4000</v>
-      </c>
-      <c r="K3">
-        <v>360</v>
-      </c>
-      <c r="L3" s="3">
-        <v>360</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>4720</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="9">
-        <v>44441</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>2000</v>
-      </c>
-      <c r="J4">
-        <v>4000</v>
-      </c>
-      <c r="K4">
-        <v>360</v>
-      </c>
-      <c r="L4" s="3">
-        <v>360</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>4720</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="G6" s="1"/>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B3" s="4"/>
+      <c r="F3" s="8"/>
+      <c r="I3" s="3"/>
+      <c r="T3" s="3"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B4" s="4"/>
+      <c r="F4" s="8"/>
+      <c r="I4" s="3"/>
+      <c r="T4" s="3"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B5" s="4"/>
+      <c r="F5" s="8"/>
+      <c r="I5" s="3"/>
+      <c r="T5" s="3"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B6" s="4"/>
+      <c r="F6" s="8"/>
+      <c r="I6" s="3"/>
+      <c r="T6" s="3"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="F8" s="8"/>
+      <c r="I8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="T8" s="3"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="F11" s="8"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="F13" s="8"/>
+      <c r="I13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="F14" s="8"/>
+      <c r="I14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="F15" s="8"/>
+      <c r="I15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="T15" s="3"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="F16" s="8"/>
+      <c r="I16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F17" s="8"/>
+      <c r="I17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="T17" s="3"/>
+    </row>
+    <row r="18" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F18" s="8"/>
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F19" s="8"/>
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F20" s="8"/>
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F21" s="8"/>
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F22" s="8"/>
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F23" s="8"/>
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F24" s="8"/>
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F25" s="8"/>
+      <c r="I25" s="3"/>
+    </row>
+    <row r="26" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F26" s="8"/>
+      <c r="I26" s="3"/>
+    </row>
+    <row r="27" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F27" s="8"/>
+      <c r="I27" s="3"/>
+    </row>
+    <row r="28" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F28" s="8"/>
+      <c r="I28" s="3"/>
+    </row>
+    <row r="29" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F29" s="8"/>
+      <c r="I29" s="3"/>
+    </row>
+    <row r="30" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F30" s="8"/>
+      <c r="I30" s="3"/>
+    </row>
+    <row r="31" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F31" s="8"/>
+      <c r="I31" s="3"/>
+    </row>
+    <row r="32" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F32" s="8"/>
+      <c r="I32" s="3"/>
+    </row>
+    <row r="33" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F33" s="8"/>
+      <c r="I33" s="3"/>
+    </row>
+    <row r="34" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F34" s="8"/>
+      <c r="I34" s="3"/>
+    </row>
+    <row r="35" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F35" s="8"/>
+      <c r="I35" s="3"/>
+    </row>
+    <row r="36" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F36" s="8"/>
+      <c r="I36" s="3"/>
+    </row>
+    <row r="37" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F37" s="8"/>
+      <c r="I37" s="3"/>
+    </row>
+    <row r="38" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F38" s="8"/>
+      <c r="I38" s="3"/>
+    </row>
+    <row r="39" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F39" s="8"/>
+      <c r="I39" s="3"/>
+    </row>
+    <row r="40" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F40" s="8"/>
+      <c r="I40" s="3"/>
+    </row>
+    <row r="41" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F41" s="8"/>
+      <c r="I41" s="3"/>
+    </row>
+    <row r="42" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F42" s="8"/>
+      <c r="I42" s="3"/>
+    </row>
+    <row r="43" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F43" s="8"/>
+      <c r="I43" s="3"/>
+    </row>
+    <row r="44" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F44" s="8"/>
+      <c r="I44" s="3"/>
+    </row>
+    <row r="45" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F45" s="8"/>
+      <c r="I45" s="3"/>
+    </row>
+    <row r="46" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F46" s="8"/>
+      <c r="I46" s="3"/>
+    </row>
+    <row r="47" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F47" s="8"/>
+      <c r="I47" s="3"/>
+    </row>
+    <row r="48" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F48" s="8"/>
+      <c r="I48" s="3"/>
+    </row>
+    <row r="49" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F49" s="8"/>
+      <c r="I49" s="3"/>
+    </row>
+    <row r="50" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F50" s="8"/>
+      <c r="I50" s="3"/>
+    </row>
+    <row r="51" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F51" s="8"/>
+      <c r="I51" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>